--- a/events/Brandenburg_2016_MAR/Brandenburg_2016_MAR_Results.xlsx
+++ b/events/Brandenburg_2016_MAR/Brandenburg_2016_MAR_Results.xlsx
@@ -1319,6 +1319,11 @@
           <t>+05:35.870</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>79361</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3177,6 +3182,11 @@
       <c r="L39" t="n">
         <v>534</v>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -3954,6 +3964,11 @@
           <t>+13:12.520</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>64815</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5008,6 +5023,11 @@
           <t>+09:15.260</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5718,6 +5738,11 @@
           <t>+03:08.220</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>64338</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6268,6 +6293,11 @@
           <t>+06.490</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6911,6 +6941,11 @@
           <t>+05:31.170</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8281,6 +8316,11 @@
           <t>+36.270</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8852,6 +8892,11 @@
           <t>+08:17.520</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>48188</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10117,6 +10162,11 @@
           <t>+04:57.850</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>88483</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10184,6 +10234,11 @@
           <t>+05:23.500</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>71704</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14783,6 +14838,11 @@
           <t>+34.800</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15066,6 +15126,11 @@
           <t>+04:30.160</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15133,6 +15198,11 @@
           <t>+05:38.240</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15760,6 +15830,11 @@
           <t>02:20:11.662</t>
         </is>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15971,6 +16046,11 @@
           <t>+02.320</t>
         </is>
       </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16686,6 +16766,11 @@
           <t>+01:42.608</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -18216,6 +18301,11 @@
       <c r="L253" t="n">
         <v>576</v>
       </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
       <c r="X253" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -19053,6 +19143,11 @@
           <t>69453</t>
         </is>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>62501</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -19274,6 +19369,11 @@
           <t>+06:06.690</t>
         </is>
       </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>71704</t>
+        </is>
+      </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>71703</t>
@@ -19500,6 +19600,11 @@
           <t>+06:17.690</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>72617</t>
+        </is>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>72557</t>
@@ -19577,6 +19682,11 @@
           <t>72031</t>
         </is>
       </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>72034</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -20629,6 +20739,11 @@
           <t>+07:11.290</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
       <c r="S285" t="inlineStr">
         <is>
           <t>71566</t>
@@ -20706,6 +20821,11 @@
           <t>79101</t>
         </is>
       </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>75056</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -23305,6 +23425,11 @@
       <c r="L321" t="n">
         <v>659</v>
       </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
       <c r="S321" t="inlineStr">
         <is>
           <t>48163</t>
@@ -23377,6 +23502,11 @@
           <t>02:06:28.698</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
       <c r="S322" t="inlineStr">
         <is>
           <t>58216</t>
@@ -23449,6 +23579,11 @@
           <t>+00.442</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S323" t="inlineStr">
         <is>
           <t>49664</t>
@@ -23757,6 +23892,11 @@
           <t>49661</t>
         </is>
       </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -24361,6 +24501,11 @@
       <c r="Q335" t="inlineStr">
         <is>
           <t>+04:36.882</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>49762</t>
         </is>
       </c>
       <c r="S335" t="inlineStr">
@@ -25266,7 +25411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32705,6 +32850,512 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>48188</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Mykhailo</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>PRYKHODKO</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>48400</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Hank</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>MCGREGOR</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Levente</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>BALLA</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Emil</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>TORSTENSSON</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>54534</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Annesofie</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>WINTHER</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>62501</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Rasmus</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>MADSEN</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Marton</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>MESZAROS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>64338</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>JANIK</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>64815</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Vanesa</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>TOT</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>COELHO</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>71704</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>CAPIN</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>72034</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>FERKINS</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>72617</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>ALONSO</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>75056</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Yaroslav</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>KHANCHEVSKYI</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>FRIEND CHUNG</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>79361</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Joke</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>PLAS</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>88483</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>MCLARIN</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Gergely</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>NAGY</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Brandenburg_2016_MAR/Brandenburg_2016_MAR_Results.xlsx
+++ b/events/Brandenburg_2016_MAR/Brandenburg_2016_MAR_Results.xlsx
@@ -964,6 +964,11 @@
           <t>+03:47.060</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>65695</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3609,6 +3614,11 @@
           <t>+05:13.450</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>76936</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9452,6 +9462,11 @@
           <t>+01:40.380</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>94098</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13168,6 +13183,11 @@
           <t>+01:20.730</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18684,6 +18704,11 @@
       <c r="R258" t="inlineStr">
         <is>
           <t>66628</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>94098</t>
         </is>
       </c>
     </row>
@@ -25411,7 +25436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33356,6 +33381,94 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>65695</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Anne Hauge</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>SØRENSEN</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>76936</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Anastasiia</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>YMELIANOVA</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>94098</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>VAN DER WESTHUIZEN</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
